--- a/docs/risk-assessment.xlsx
+++ b/docs/risk-assessment.xlsx
@@ -21,6 +21,8 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Assets!$A$1:$J$19</definedName>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Control Map'!$A$3:$G$27</definedName>
+    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'Evidence Tracker'!$A$3:$I$27</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'Remediation Plan'!$A$3:$J$24</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Risk Register'!$A$1:$N$16</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="679">
   <si>
     <t xml:space="preserve">Risk Assessment Workbook: Anita &amp; Daughters (Fictional)</t>
   </si>
@@ -116,9 +118,6 @@
     <t xml:space="preserve">6</t>
   </si>
   <si>
-    <t xml:space="preserve">To fill in</t>
-  </si>
-  <si>
     <t xml:space="preserve">Evidence Tracker</t>
   </si>
   <si>
@@ -1499,10 +1498,10 @@
     <t xml:space="preserve">Restores have never been tested, and no integrity checks are done (S-05)</t>
   </si>
   <si>
-    <t xml:space="preserve">Remediation Plan: fill in during Phase 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One row per gap (a control marked Partial or Missing). Rank by the highest linked risk score. Delete the yellow example row when you add your own.</t>
+    <t xml:space="preserve">Remediation Plan (Phase 6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One row per gap: a control marked Partial or Missing on the Control Map. Priority follows the highest linked risk score: P1 = Critical (17 to 25), P2 = High (10 to 16), P3 = Medium or Low (below 10). Target dates start 2026-11-01. Update Status as work is done.</t>
   </si>
   <si>
     <t xml:space="preserve">Gap ID</t>
@@ -1529,10 +1528,13 @@
     <t xml:space="preserve">Success measure</t>
   </si>
   <si>
-    <t xml:space="preserve">EXAMPLE: GAP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turn on MFA for all staff Microsoft 365 accounts</t>
+    <t xml:space="preserve">Plan check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turn on MFA for all 50 staff Microsoft 365 accounts and require MFA on the VPN</t>
   </si>
   <si>
     <t xml:space="preserve">P1</t>
@@ -1541,13 +1543,223 @@
     <t xml:space="preserve">Not started</t>
   </si>
   <si>
-    <t xml:space="preserve">100% of staff accounts show MFA registered in the sign-in report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mock Audit Evidence Tracker: fill in during Phase 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For each control, list the proof an auditor would ask for. Delete the yellow example row when you add your own.</t>
+    <t xml:space="preserve">100% of staff accounts and VPN logins show MFA registered in the sign-in report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1 actions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run the first training for all staff in English and Thai, including a phishing test; repeat every year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 of 50 staff completed training (records kept); phishing test click rate recorded as the baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2 actions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test restoring the file server from backup, and replace the shared backup console password with named admin accounts that use MFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restore test record shows date, what was restored, and pass or fail; the console shows 0 shared accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3 actions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enroll all laptops in a central device management tool with a standard security setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 of 50 devices appear in the management console with the standard setup applied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total actions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patch the file server every month and turn on automatic updates on all laptops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patch log shows a monthly patch; 0 critical updates older than 30 days on the server or laptops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaps on Control Map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scan the file server, firewall, and laptops for weaknesses every quarter, and fix serious findings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First scan report is on file; every Critical and High finding is fixed or accepted in writing within 30 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every gap covered?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review and tighten the firewall settings, close unneeded ports, and limit VPN access to named users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firewall review is signed by the IT Manager; 0 unneeded open ports; VPN user list matches the staff roster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give each Claims team member their own clearinghouse login, or record an approved exception if the portal does not allow it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 shared logins on the clearinghouse portal; the user list matches the roster, or an approved exception is on file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write step-by-step recovery instructions for the file server, Microsoft 365, and billing platform, with the order and who does each step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runbook is approved by the COO and one walkthrough has been done and written up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check backups for damage before restoring, and put two restore tests per year on the calendar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The first integrity check is recorded; the next two restore tests are scheduled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turn on full-disk encryption for the remaining devices (about 38 of 50) and store the recovery keys safely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 of 50 devices report encryption on; recovery keys are stored for every device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start a joiner-mover-leaver checklist with HR, limit the contracts folder to the people who need it, and hold the first quarterly access review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First review is signed by all 7 managers; contracts folder access list is limited to named people; 0 leaver accounts still active in the review sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approve and publish the three Phase 5 policies, and collect a signed acknowledgment from every employee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 policies signed by the CEO; 50 of 50 acknowledgments on file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write down the incident roles (incident, technical, privacy, communications) and a backup for each, and tell all staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles and backups are named in the Incident Response Policy; 50 of 50 staff acknowledge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create the incident record template and hold the first practice drill with a made-up scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template exists; first drill is held and written up with lessons learned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build the incident contact list and notification checklist, and record each client contract's notice deadline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact list is reviewed and dated; every client contract's deadline is recorded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add security terms to the help desk contract (named accounts, MFA, breach notice) and get the payment processor's security attestation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signed contract amendment on file; processor attestation on file and less than 12 months old</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turn on Microsoft 365 sign-in alerts and review the sign-in logs every week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alert rules are active; a weekly review is logged for 8 weeks in a row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write a one-page procedure for checking an alert: who looks, what to check, and when to start the incident plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedure is approved; one test alert is handled from start to finish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train payroll and finance staff to spot fake bank-detail change requests, and require a call-back to a known number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 6 Finance and HR staff trained; every bank change in the next 3 months has a call-back note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAP-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Put locks on the claim cabinets, add shredding bins, and shred old paper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly spot check for 3 months: 100% of cabinets locked and 0 claim papers in the recycling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mock Audit Evidence Tracker (Phase 7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One row per Control Map control. "Evidence" is what an auditor would ask to see. Status is pulled from the Control Map (Implemented shows as Available), and Linked gap is pulled from the Remediation Plan. Folder paths are an invented shared-drive layout for this fictional firm.</t>
   </si>
   <si>
     <t xml:space="preserve">Control (CSF ID)</t>
@@ -1565,22 +1777,301 @@
     <t xml:space="preserve">How often</t>
   </si>
   <si>
-    <t xml:space="preserve">EXAMPLE: PR.AA-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Access is reviewed and kept to what each job needs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quarterly user access review, signed by each manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shared drive: Compliance / Access Reviews</t>
+    <t xml:space="preserve">Linked gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Someone is named responsible for security, and everyone knows who</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signed Incident Response Policy naming each role holder and a backup; staff acknowledgment of the roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance / Policies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yearly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The COO is an informal contact only. No written roles yet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The company has written security policies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three approved policies signed by the CEO, with version history; signed acknowledgment from every employee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drafts exist from Phase 5 but are not yet approved or signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendors must meet security requirements written into contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk contract amendment with security terms; payment processor security attestation; vendor list with review dates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance / Vendors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neither the contract terms nor the attestation exist today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The company keeps a list of its systems and assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current asset inventory with an owner and a last-reviewed date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance / Risk Assessment (Assets tab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twice a year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inventory was built in this assessment. It needs an owner to keep it current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets are ranked by sensitivity and importance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification and criticality score for every asset, with the scoring method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance / Risk Assessment (Assets and Scoring Guide tabs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 18 assets are classified and scored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control Map total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vulnerability scan reports and a list showing how each serious finding was fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT / Vulnerability Scans</t>
   </si>
   <si>
     <t xml:space="preserve">Quarterly</t>
   </si>
   <si>
-    <t xml:space="preserve">No review has been done yet</t>
+    <t xml:space="preserve">Weaknesses are recorded in this assessment only. No scans have been run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every control listed?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risks are ranked using likelihood and impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risk register with scores, the scoring method, and the date it was last reviewed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance / Risk Assessment (Risk Register tab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 risks scored. Add a CEO review date at the next update</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controls with a linked gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each person has their own account and login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User list for each system matched to the staff roster; log of approved exceptions for shared accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT / Access Evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft 365 accounts are individual. The clearinghouse portal and backup console are shared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaps in the plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People prove who they are before getting access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign-in report showing MFA registered for every user; screenshot of the VPN MFA setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFA covers only the 2 IT admin accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access is limited to the job and reviewed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarterly access review signed by each manager; leaver tickets with the time each account was disabled; contracts folder permission list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance / Access Reviews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No review has ever been done, and all staff can read the contracts folder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical access to the office and paper records is controlled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photos of locked cabinets; key log; shredding bin pickup receipts; monthly spot-check sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance / Physical Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The office door is locked after hours. Cabinets of printed claims are not locked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff get security training that fits their jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training roster by name and date; English and Thai training materials; phishing test results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR / Training Records</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training was given once at hire, in English only. No refresher since 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People in special roles get training for their risks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payroll and finance training sign-in sheet; call-back notes for bank-detail changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No fraud training has been given. Bank changes are accepted by email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device management report showing encryption status for every device; proof the recovery keys are stored safely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT / Devices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About 12 of 50 devices are encrypted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backups are made, protected, and tested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup job reports; restore test records; list of people who can use the backup console</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT / Backups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nightly backups run. Restores are untested and the console password is shared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device management console export showing every device; the written standard setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No central management or standard setup exists for laptops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software is kept up to date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File server patch log; laptop update compliance report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT / Patching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The file server is patched irregularly. Staff update laptops when prompted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firewall rule review signed by IT; VPN user list; firewall settings export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT / Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The firewall runs on default settings and the VPN accepts a password alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff activity is watched for signs of trouble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screenshot of alert rules; weekly log of sign-in report reviews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT / Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No one reviews Microsoft 365 sign-in logs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suspicious events are analyzed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Written alert-checking procedure; tickets showing an alert was analyzed and closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each alert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No process exists for analyzing alerts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The incident plan is carried out when an incident is declared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incident records; drill report; post-incident review notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance / Incidents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each incident and yearly drill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No written plan, so nothing has been recorded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The right people are told about incidents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact list with a review date; table of client notice deadlines; copies of notices sent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No contact list or notification steps exist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Written recovery runbook; record of a walkthrough of it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT / Recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No written restore steps exist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backups are checked for damage before restoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrity check record before each restore; restore test log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restores have never been tested and no integrity checks are done</t>
   </si>
 </sst>
 </file>
@@ -1596,7 +2087,7 @@
     <numFmt numFmtId="169" formatCode="0;\-0;\-"/>
     <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1678,16 +2169,8 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1715,19 +2198,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE599"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFCE4B0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB6D7A8"/>
-        <bgColor rgb="FFBFBFBF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFC6E0B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -1780,20 +2257,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1833,47 +2314,47 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1881,7 +2362,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1905,7 +2386,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1913,16 +2394,20 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1934,7 +2419,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2026,6 +2511,65 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2EFDA"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4B0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4B0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6E0B4"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4B0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4B6B6"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -2047,12 +2591,12 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFFCE4B0"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFB6D7A8"/>
+      <rgbColor rgb="FFC6E0B4"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -2063,9 +2607,9 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFE599"/>
-      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFB6D7A8"/>
       <rgbColor rgb="FFF4B6B6"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFF9CB9C"/>
@@ -2099,6 +2643,14 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -2285,197 +2837,197 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-    </row>
-    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2503,640 +3055,640 @@
   <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="7" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J2" s="8" t="n">
+      <c r="J2" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A2)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="8" t="n">
+      <c r="J3" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A3)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4" s="8" t="n">
+      <c r="J4" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A4)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A5)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J6" s="8" t="n">
+      <c r="J6" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A6)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="H7" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="H7" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="J7" s="8" t="n">
+      <c r="J7" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A7)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" s="8" t="n">
+      <c r="J8" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A8)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="8" t="n">
+      <c r="J9" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J10" s="8" t="n">
+      <c r="J10" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A10)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="J11" s="8" t="n">
+      <c r="J11" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="H12" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="H12" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="J12" s="8" t="n">
+      <c r="J12" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A12)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="J13" s="8" t="n">
+      <c r="J13" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A13)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" s="9" t="n">
+      <c r="H15" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="J15" s="8" t="n">
+      <c r="I15" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="J15" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A15)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="J16" s="8" t="n">
+      <c r="J16" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A16)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H17" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J17" s="8" t="n">
+      <c r="J17" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A17)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="J18" s="8" t="n">
+      <c r="J18" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A18)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="J19" s="8" t="n">
+      <c r="J19" s="9" t="n">
         <f aca="false">COUNTIF('Risk Register'!$B$2:$B$16,A19)</f>
         <v>3</v>
       </c>
@@ -3172,289 +3724,289 @@
   <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="7" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="D5" s="8" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="D6" s="8" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="8" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="8" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="8" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="8" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D11" s="8" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="B12" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="8" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D14" s="8" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="B15" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D15" s="8" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="B16" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="8" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" s="8" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="D18" s="8" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D19" s="8" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" s="8" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
+      <c r="B21" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="D21" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="D21" s="8" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>169</v>
+      <c r="D22" s="9" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -3479,437 +4031,437 @@
   <dimension ref="A1:D48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="D4" s="7" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="n">
+      <c r="C5" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="n">
+      <c r="B13" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="n">
+      <c r="B14" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="n">
+      <c r="B15" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="n">
+      <c r="B16" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="B17" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B23" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+    </row>
+    <row r="31" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C35" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="n">
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="n">
+      <c r="B36" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="n">
+      <c r="B37" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="n">
+      <c r="B38" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="D38" s="6"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="n">
+      <c r="B39" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="B23" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="B24" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-    </row>
-    <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-    </row>
-    <row r="31" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B35" s="7" t="s">
+      <c r="B40" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="D40" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D35" s="7"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D36" s="5"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="D37" s="5"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="D38" s="5"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D39" s="5"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D40" s="5"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="s">
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+    </row>
+    <row r="44" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-    </row>
-    <row r="44" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-    </row>
-    <row r="45" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B45" s="5" t="s">
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-    </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B46" s="5" t="s">
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-    </row>
-    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3933,749 +4485,749 @@
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="N1" s="7" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C2" s="5" t="str">
+    </row>
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B2,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Staff user accounts</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="G2" s="9" t="n">
+      <c r="G2" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="9" t="n">
+      <c r="H2" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I2" s="8" t="n">
+      <c r="I2" s="9" t="n">
         <f aca="false">G2*H2</f>
         <v>20</v>
       </c>
-      <c r="J2" s="8" t="str">
+      <c r="J2" s="9" t="str">
         <f aca="false">IF(I2&gt;='Scoring Guide'!$B$24,"Critical",IF(I2&gt;='Scoring Guide'!$B$23,"High",IF(I2&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>Critical</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="N2" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="L2" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="5" t="str">
+    </row>
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B3,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Office file server</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G3" s="9" t="n">
+      <c r="G3" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="9" t="n">
+      <c r="H3" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="9" t="n">
         <f aca="false">G3*H3</f>
         <v>20</v>
       </c>
-      <c r="J3" s="8" t="str">
+      <c r="J3" s="9" t="str">
         <f aca="false">IF(I3&gt;='Scoring Guide'!$B$24,"Critical",IF(I3&gt;='Scoring Guide'!$B$23,"High",IF(I3&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>Critical</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="L3" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="5" t="str">
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B4,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Cloud backup service</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="H4" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I4" s="8" t="n">
+      <c r="I4" s="9" t="n">
         <f aca="false">G4*H4</f>
         <v>15</v>
       </c>
-      <c r="J4" s="8" t="str">
+      <c r="J4" s="9" t="str">
         <f aca="false">IF(I4&gt;='Scoring Guide'!$B$24,"Critical",IF(I4&gt;='Scoring Guide'!$B$23,"High",IF(I4&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>High</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="N4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="5" t="str">
+      <c r="K4" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B5,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Staff laptops and desktops (about 50)</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="9" t="n">
         <f aca="false">G5*H5</f>
         <v>12</v>
       </c>
-      <c r="J5" s="8" t="str">
+      <c r="J5" s="9" t="str">
         <f aca="false">IF(I5&gt;='Scoring Guide'!$B$24,"Critical",IF(I5&gt;='Scoring Guide'!$B$23,"High",IF(I5&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>High</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="N5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" s="5" t="str">
+      <c r="K5" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B6,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>VPN</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="9" t="n">
         <f aca="false">G6*H6</f>
         <v>16</v>
       </c>
-      <c r="J6" s="8" t="str">
+      <c r="J6" s="9" t="str">
         <f aca="false">IF(I6&gt;='Scoring Guide'!$B$24,"Critical",IF(I6&gt;='Scoring Guide'!$B$23,"High",IF(I6&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>High</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="N6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="5" t="str">
+      <c r="K6" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B7,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Clearinghouse portal</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="9" t="n">
         <f aca="false">G7*H7</f>
         <v>12</v>
       </c>
-      <c r="J7" s="8" t="str">
+      <c r="J7" s="9" t="str">
         <f aca="false">IF(I7&gt;='Scoring Guide'!$B$24,"Critical",IF(I7&gt;='Scoring Guide'!$B$23,"High",IF(I7&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>High</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="N7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="5" t="str">
+      <c r="K7" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B8,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Staff user accounts</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="9" t="n">
         <f aca="false">G8*H8</f>
         <v>12</v>
       </c>
-      <c r="J8" s="8" t="str">
+      <c r="J8" s="9" t="str">
         <f aca="false">IF(I8&gt;='Scoring Guide'!$B$24,"Critical",IF(I8&gt;='Scoring Guide'!$B$23,"High",IF(I8&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>High</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="L8" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="5" t="str">
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B9,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Outside IT help desk</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="8" t="n">
+      <c r="I9" s="9" t="n">
         <f aca="false">G9*H9</f>
         <v>10</v>
       </c>
-      <c r="J9" s="8" t="str">
+      <c r="J9" s="9" t="str">
         <f aca="false">IF(I9&gt;='Scoring Guide'!$B$24,"Critical",IF(I9&gt;='Scoring Guide'!$B$23,"High",IF(I9&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>High</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="L9" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="N9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="5" t="str">
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B10,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Microsoft 365 tenant</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="8" t="n">
+      <c r="I10" s="9" t="n">
         <f aca="false">G10*H10</f>
         <v>9</v>
       </c>
-      <c r="J10" s="8" t="str">
+      <c r="J10" s="9" t="str">
         <f aca="false">IF(I10&gt;='Scoring Guide'!$B$24,"Critical",IF(I10&gt;='Scoring Guide'!$B$23,"High",IF(I10&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>Medium</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="N10" s="5"/>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="5" t="str">
+      <c r="K10" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B11,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Practice management and billing platform</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" s="9" t="n">
         <f aca="false">G11*H11</f>
         <v>12</v>
       </c>
-      <c r="J11" s="8" t="str">
+      <c r="J11" s="9" t="str">
         <f aca="false">IF(I11&gt;='Scoring Guide'!$B$24,"Critical",IF(I11&gt;='Scoring Guide'!$B$23,"High",IF(I11&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>High</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="N11" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C12" s="5" t="str">
+      <c r="K11" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B12,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Payment processor</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="I12" s="9" t="n">
         <f aca="false">G12*H12</f>
         <v>8</v>
       </c>
-      <c r="J12" s="8" t="str">
+      <c r="J12" s="9" t="str">
         <f aca="false">IF(I12&gt;='Scoring Guide'!$B$24,"Critical",IF(I12&gt;='Scoring Guide'!$B$23,"High",IF(I12&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>Medium</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="N12" s="5"/>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="5" t="str">
+      <c r="K12" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B13,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Accounting and payroll software</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="H13" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I13" s="9" t="n">
         <f aca="false">G13*H13</f>
         <v>9</v>
       </c>
-      <c r="J13" s="8" t="str">
+      <c r="J13" s="9" t="str">
         <f aca="false">IF(I13&gt;='Scoring Guide'!$B$24,"Critical",IF(I13&gt;='Scoring Guide'!$B$23,"High",IF(I13&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>Medium</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="N13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="5" t="str">
+      <c r="K13" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B14,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Printed claim documents and patient statements</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="9" t="n">
+      <c r="H14" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="I14" s="9" t="n">
         <f aca="false">G14*H14</f>
         <v>6</v>
       </c>
-      <c r="J14" s="8" t="str">
+      <c r="J14" s="9" t="str">
         <f aca="false">IF(I14&gt;='Scoring Guide'!$B$24,"Critical",IF(I14&gt;='Scoring Guide'!$B$23,"High",IF(I14&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>Medium</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="L14" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="N14" s="5"/>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C15" s="5" t="str">
+      <c r="B15" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B15,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Staff user accounts</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="H15" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="9" t="n">
         <f aca="false">G15*H15</f>
         <v>6</v>
       </c>
-      <c r="J15" s="8" t="str">
+      <c r="J15" s="9" t="str">
         <f aca="false">IF(I15&gt;='Scoring Guide'!$B$24,"Critical",IF(I15&gt;='Scoring Guide'!$B$23,"High",IF(I15&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>Medium</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K15" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="N15" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="L15" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" s="5" t="str">
+    </row>
+    <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Assets!$B$2:$B$19,MATCH(B16,Assets!$A$2:$A$19,0)),"Check asset ID")</f>
         <v>Client contracts and pricing</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="9" t="n">
+      <c r="H16" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="8" t="n">
+      <c r="I16" s="9" t="n">
         <f aca="false">G16*H16</f>
         <v>4</v>
       </c>
-      <c r="J16" s="8" t="str">
+      <c r="J16" s="9" t="str">
         <f aca="false">IF(I16&gt;='Scoring Guide'!$B$24,"Critical",IF(I16&gt;='Scoring Guide'!$B$23,"High",IF(I16&gt;='Scoring Guide'!$B$22,"Medium","Low")))</f>
         <v>Low</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="N16" s="6" t="s">
         <v>356</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -4727,412 +5279,412 @@
   <dimension ref="A1:J36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="I3" s="3" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="B4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="J4" s="14" t="n">
+      <c r="I4" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="J4" s="15" t="n">
         <f aca="false">'Scoring Guide'!$B$24</f>
         <v>17</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="B5" s="13" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="14" t="n">
         <f aca="false">COUNTIF('Risk Register'!$J$2:$J$16,A5)</f>
         <v>2</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <f aca="false">IF($B$9=0,0,B5/$B$9)</f>
         <v>0.133333333333333</v>
       </c>
-      <c r="I5" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="J5" s="14" t="n">
+      <c r="I5" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="J5" s="15" t="n">
         <f aca="false">'Scoring Guide'!$B$23</f>
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="B6" s="13" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6" s="14" t="n">
         <f aca="false">COUNTIF('Risk Register'!$J$2:$J$16,A6)</f>
         <v>7</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <f aca="false">IF($B$9=0,0,B6/$B$9)</f>
         <v>0.466666666666667</v>
       </c>
-      <c r="I6" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="J6" s="14" t="n">
+      <c r="I6" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="J6" s="15" t="n">
         <f aca="false">'Scoring Guide'!$B$22</f>
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="B7" s="13" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="B7" s="14" t="n">
         <f aca="false">COUNTIF('Risk Register'!$J$2:$J$16,A7)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <f aca="false">IF($B$9=0,0,B7/$B$9)</f>
         <v>0.333333333333333</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="B8" s="13" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="B8" s="14" t="n">
         <f aca="false">COUNTIF('Risk Register'!$J$2:$J$16,A8)</f>
         <v>1</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <f aca="false">IF($B$9=0,0,B8/$B$9)</f>
         <v>0.0666666666666667</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="B9" s="20" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="B9" s="21" t="n">
         <f aca="false">SUM(B5:B8)</f>
         <v>15</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="22" t="n">
         <f aca="false">SUM(C5:C8)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="23" t="n">
         <f aca="false">COUNTA('Risk Register'!$A$2:$A$16)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="B13" s="23" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="B13" s="24" t="n">
         <f aca="false">AVERAGE('Risk Register'!$I$2:$I$16)</f>
         <v>11.4</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="B14" s="22" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B14" s="23" t="n">
         <f aca="false">MAX('Risk Register'!$I$2:$I$16)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="B15" s="22" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="B15" s="23" t="n">
         <f aca="false">COUNTA(Assets!$A$2:$A$19)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="B16" s="22" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="B16" s="23" t="n">
         <f aca="false">COUNTIF(Assets!$G$2:$G$19,"Restricted")</f>
         <v>15</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="B17" s="22" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="B17" s="23" t="n">
         <f aca="false">COUNTIF(Assets!$J$2:$J$19,0)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="B21" s="13" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="B21" s="14" t="n">
         <f aca="false">COUNTIF('Risk Register'!$L$2:$L$16,A21)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="B22" s="13" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B22" s="14" t="n">
         <f aca="false">COUNTIF('Risk Register'!$L$2:$L$16,A22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="B23" s="13" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="B23" s="14" t="n">
         <f aca="false">COUNTIF('Risk Register'!$L$2:$L$16,A23)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="B24" s="13" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B24" s="14" t="n">
         <f aca="false">COUNTIF('Risk Register'!$L$2:$L$16,A24)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C28" s="25" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="24" t="s">
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="26" t="s">
         <v>373</v>
       </c>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="25" t="s">
-        <v>374</v>
-      </c>
-      <c r="B29" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="C29" s="12" t="n">
+      <c r="B29" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="C29" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="F29" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="G29" s="13" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="B30" s="27" t="n">
+      <c r="A30" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="B30" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="28" t="n">
+      <c r="C30" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,C$29,'Risk Register'!$H$2:$H$16,$B30)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="28" t="n">
+      <c r="D30" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,D$29,'Risk Register'!$H$2:$H$16,$B30)</f>
         <v>1</v>
       </c>
-      <c r="E30" s="28" t="n">
+      <c r="E30" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,E$29,'Risk Register'!$H$2:$H$16,$B30)</f>
         <v>1</v>
       </c>
-      <c r="F30" s="28" t="n">
+      <c r="F30" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,F$29,'Risk Register'!$H$2:$H$16,$B30)</f>
         <v>1</v>
       </c>
-      <c r="G30" s="28" t="n">
+      <c r="G30" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,G$29,'Risk Register'!$H$2:$H$16,$B30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="B31" s="27" t="n">
+      <c r="A31" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="C31" s="28" t="n">
+      <c r="C31" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,C$29,'Risk Register'!$H$2:$H$16,$B31)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="28" t="n">
+      <c r="D31" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,D$29,'Risk Register'!$H$2:$H$16,$B31)</f>
         <v>1</v>
       </c>
-      <c r="E31" s="28" t="n">
+      <c r="E31" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,E$29,'Risk Register'!$H$2:$H$16,$B31)</f>
         <v>4</v>
       </c>
-      <c r="F31" s="28" t="n">
+      <c r="F31" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,F$29,'Risk Register'!$H$2:$H$16,$B31)</f>
         <v>1</v>
       </c>
-      <c r="G31" s="28" t="n">
+      <c r="G31" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,G$29,'Risk Register'!$H$2:$H$16,$B31)</f>
         <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="B32" s="27" t="n">
+      <c r="A32" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="B32" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="28" t="n">
+      <c r="C32" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,C$29,'Risk Register'!$H$2:$H$16,$B32)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="28" t="n">
+      <c r="D32" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,D$29,'Risk Register'!$H$2:$H$16,$B32)</f>
         <v>1</v>
       </c>
-      <c r="E32" s="28" t="n">
+      <c r="E32" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,E$29,'Risk Register'!$H$2:$H$16,$B32)</f>
         <v>2</v>
       </c>
-      <c r="F32" s="28" t="n">
+      <c r="F32" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,F$29,'Risk Register'!$H$2:$H$16,$B32)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="28" t="n">
+      <c r="G32" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,G$29,'Risk Register'!$H$2:$H$16,$B32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="B33" s="27" t="n">
+      <c r="A33" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="B33" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="28" t="n">
+      <c r="C33" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,C$29,'Risk Register'!$H$2:$H$16,$B33)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="28" t="n">
+      <c r="D33" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,D$29,'Risk Register'!$H$2:$H$16,$B33)</f>
         <v>1</v>
       </c>
-      <c r="E33" s="28" t="n">
+      <c r="E33" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,E$29,'Risk Register'!$H$2:$H$16,$B33)</f>
         <v>1</v>
       </c>
-      <c r="F33" s="28" t="n">
+      <c r="F33" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,F$29,'Risk Register'!$H$2:$H$16,$B33)</f>
         <v>0</v>
       </c>
-      <c r="G33" s="28" t="n">
+      <c r="G33" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,G$29,'Risk Register'!$H$2:$H$16,$B33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="B34" s="27" t="n">
+      <c r="A34" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="B34" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="28" t="n">
+      <c r="C34" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,C$29,'Risk Register'!$H$2:$H$16,$B34)</f>
         <v>0</v>
       </c>
-      <c r="D34" s="28" t="n">
+      <c r="D34" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,D$29,'Risk Register'!$H$2:$H$16,$B34)</f>
         <v>0</v>
       </c>
-      <c r="E34" s="28" t="n">
+      <c r="E34" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,E$29,'Risk Register'!$H$2:$H$16,$B34)</f>
         <v>0</v>
       </c>
-      <c r="F34" s="28" t="n">
+      <c r="F34" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,F$29,'Risk Register'!$H$2:$H$16,$B34)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="28" t="n">
+      <c r="G34" s="29" t="n">
         <f aca="false">COUNTIFS('Risk Register'!$G$2:$G$16,G$29,'Risk Register'!$H$2:$H$16,$B34)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
-        <v>375</v>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -5171,760 +5723,760 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="I2" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="I2" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="I3" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="8" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="M3" s="7" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="J4" s="29" t="n">
+      <c r="G4" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="J4" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I4,$E$4:$E$60,J$3)</f>
         <v>0</v>
       </c>
-      <c r="K4" s="29" t="n">
+      <c r="K4" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I4,$E$4:$E$60,K$3)</f>
         <v>1</v>
       </c>
-      <c r="L4" s="29" t="n">
+      <c r="L4" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I4,$E$4:$E$60,L$3)</f>
         <v>2</v>
       </c>
-      <c r="M4" s="29" t="n">
+      <c r="M4" s="30" t="n">
         <f aca="false">SUM(J4:L4)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="B5" s="8" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="I5" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="J5" s="29" t="n">
+      <c r="J5" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I5,$E$4:$E$60,J$3)</f>
         <v>3</v>
       </c>
-      <c r="K5" s="29" t="n">
+      <c r="K5" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I5,$E$4:$E$60,K$3)</f>
         <v>1</v>
       </c>
-      <c r="L5" s="29" t="n">
+      <c r="L5" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I5,$E$4:$E$60,L$3)</f>
         <v>0</v>
       </c>
-      <c r="M5" s="29" t="n">
+      <c r="M5" s="30" t="n">
         <f aca="false">SUM(J5:L5)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="B6" s="8" t="s">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="I6" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="I6" s="13" t="s">
-        <v>403</v>
-      </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I6,$E$4:$E$60,J$3)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="29" t="n">
+      <c r="K6" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I6,$E$4:$E$60,K$3)</f>
         <v>8</v>
       </c>
-      <c r="L6" s="29" t="n">
+      <c r="L6" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I6,$E$4:$E$60,L$3)</f>
         <v>3</v>
       </c>
-      <c r="M6" s="29" t="n">
+      <c r="M6" s="30" t="n">
         <f aca="false">SUM(J6:L6)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="B7" s="8" t="s">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="I7" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="J7" s="29" t="n">
+      <c r="J7" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I7,$E$4:$E$60,J$3)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="29" t="n">
+      <c r="K7" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I7,$E$4:$E$60,K$3)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="29" t="n">
+      <c r="L7" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I7,$E$4:$E$60,L$3)</f>
         <v>2</v>
       </c>
-      <c r="M7" s="29" t="n">
+      <c r="M7" s="30" t="n">
         <f aca="false">SUM(J7:L7)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="C8" s="8" t="s">
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="I8" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>412</v>
-      </c>
-      <c r="J8" s="29" t="n">
+      <c r="J8" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I8,$E$4:$E$60,J$3)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="29" t="n">
+      <c r="K8" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I8,$E$4:$E$60,K$3)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="29" t="n">
+      <c r="L8" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I8,$E$4:$E$60,L$3)</f>
         <v>2</v>
       </c>
-      <c r="M8" s="29" t="n">
+      <c r="M8" s="30" t="n">
         <f aca="false">SUM(J8:L8)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="B9" s="8" t="s">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="I9" s="14" t="s">
         <v>417</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>418</v>
-      </c>
-      <c r="J9" s="29" t="n">
+      <c r="J9" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I9,$E$4:$E$60,J$3)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="29" t="n">
+      <c r="K9" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I9,$E$4:$E$60,K$3)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="29" t="n">
+      <c r="L9" s="30" t="n">
         <f aca="false">COUNTIFS($A$4:$A$60,$I9,$E$4:$E$60,L$3)</f>
         <v>2</v>
       </c>
-      <c r="M9" s="29" t="n">
+      <c r="M9" s="30" t="n">
         <f aca="false">SUM(J9:L9)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>413</v>
-      </c>
-      <c r="C10" s="8" t="s">
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="I10" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="J10" s="30" t="n">
+      <c r="G10" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="J10" s="31" t="n">
         <f aca="false">SUM(J4:J9)</f>
         <v>3</v>
       </c>
-      <c r="K10" s="30" t="n">
+      <c r="K10" s="31" t="n">
         <f aca="false">SUM(K4:K9)</f>
         <v>10</v>
       </c>
-      <c r="L10" s="30" t="n">
+      <c r="L10" s="31" t="n">
         <f aca="false">SUM(L4:L9)</f>
         <v>11</v>
       </c>
-      <c r="M10" s="30" t="n">
+      <c r="M10" s="31" t="n">
         <f aca="false">SUM(M4:M9)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="B11" s="8" t="s">
+    <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="G11" s="8" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="I12" s="32" t="s">
         <v>430</v>
       </c>
-      <c r="I12" s="31" t="s">
-        <v>431</v>
-      </c>
-      <c r="M12" s="32" t="n">
+      <c r="M12" s="33" t="n">
         <f aca="false">K10+L10</f>
         <v>21</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="C13" s="8" t="s">
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="G13" s="8" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="G14" s="9" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="F16" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="F19" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="F22" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="E20" s="8" t="s">
+      <c r="F23" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="E21" s="8" t="s">
+      <c r="F24" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="F25" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="G25" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="B26" s="8" t="s">
+      <c r="C26" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="D26" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="C27" s="8" t="s">
+      <c r="D27" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>175</v>
+      <c r="G27" s="9" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -5962,94 +6514,801 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="L3" s="32" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H4" s="34" t="n">
+        <v>46371</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="L4" s="35" t="s">
+        <v>503</v>
+      </c>
+      <c r="M4" s="35" t="n">
+        <f aca="false">COUNTIF($E$4:$E$60,"P1")</f>
         <v>6</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>499</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>427</v>
-      </c>
-      <c r="E4" s="34" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="F4" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="H4" s="35" t="n">
-        <v>46371</v>
-      </c>
-      <c r="I4" s="34" t="s">
+      <c r="F5" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H5" s="34" t="n">
+        <v>46374</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="J4" s="33" t="s">
-        <v>502</v>
+      <c r="J5" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="L5" s="35" t="s">
+        <v>507</v>
+      </c>
+      <c r="M5" s="35" t="n">
+        <f aca="false">COUNTIF($E$4:$E$60,"P2")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H6" s="34" t="n">
+        <v>46356</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="L6" s="35" t="s">
+        <v>511</v>
+      </c>
+      <c r="M6" s="35" t="n">
+        <f aca="false">COUNTIF($E$4:$E$60,"P3")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="H7" s="34" t="n">
+        <v>46416</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="L7" s="35" t="s">
+        <v>516</v>
+      </c>
+      <c r="M7" s="35" t="n">
+        <f aca="false">COUNTA($A$4:$A$60)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H8" s="34" t="n">
+        <v>46387</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="L8" s="35" t="s">
+        <v>520</v>
+      </c>
+      <c r="M8" s="35" t="n">
+        <f aca="false">'Control Map'!M12</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H9" s="34" t="n">
+        <v>46402</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="L9" s="35" t="s">
+        <v>524</v>
+      </c>
+      <c r="M9" s="35" t="str">
+        <f aca="false">IF(M7=M8,"Yes","No: check rows")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H10" s="34" t="n">
+        <v>46430</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="L10" s="35" t="s">
+        <v>501</v>
+      </c>
+      <c r="M10" s="35" t="n">
+        <f aca="false">COUNTIF($I$4:$I$60,"Not started")</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="H11" s="34" t="n">
+        <v>46402</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H12" s="34" t="n">
+        <v>46444</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="H13" s="34" t="n">
+        <v>46444</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H14" s="34" t="n">
+        <v>46458</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H15" s="34" t="n">
+        <v>46444</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="H16" s="34" t="n">
+        <v>46356</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="H17" s="34" t="n">
+        <v>46356</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H18" s="34" t="n">
+        <v>46477</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="H19" s="34" t="n">
+        <v>46374</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H20" s="34" t="n">
+        <v>46477</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="H21" s="34" t="n">
+        <v>46507</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="H22" s="34" t="n">
+        <v>46507</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="H23" s="34" t="n">
+        <v>46477</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="H24" s="34" t="n">
+        <v>46477</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>572</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:J24"/>
+  <conditionalFormatting sqref="E4:E60">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>"P1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+      <formula>"P2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>"P3"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E4:E60" type="list">
       <formula1>"P1,P2,P3"</formula1>
@@ -6071,6 +7330,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6079,81 +7339,877 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>506</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="G3" s="7" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="s">
-        <v>510</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>511</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>512</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>513</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>326</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>514</v>
-      </c>
-      <c r="G4" s="34" t="s">
-        <v>387</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>515</v>
+      <c r="H3" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="K3" s="36" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="G4" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A4,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A4,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Partial</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="I4" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A4,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-14</v>
+      </c>
+      <c r="K4" s="37" t="s">
+        <v>587</v>
+      </c>
+      <c r="L4" s="37" t="n">
+        <f aca="false">COUNTIF($G$4:$G$60,"Available")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="G5" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A5,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A5,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Missing</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="I5" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A5,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-13</v>
+      </c>
+      <c r="K5" s="37" t="s">
+        <v>385</v>
+      </c>
+      <c r="L5" s="37" t="n">
+        <f aca="false">COUNTIF($G$4:$G$60,"Partial")</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="G6" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A6,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A6,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Missing</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="I6" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A6,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-17</v>
+      </c>
+      <c r="K6" s="37" t="s">
+        <v>386</v>
+      </c>
+      <c r="L6" s="37" t="n">
+        <f aca="false">COUNTIF($G$4:$G$60,"Missing")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="G7" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A7,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A7,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Available</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="I7" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A7,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>None needed</v>
+      </c>
+      <c r="K7" s="37" t="s">
+        <v>600</v>
+      </c>
+      <c r="L7" s="37" t="n">
+        <f aca="false">COUNTA($A$4:$A$60)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="G8" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A8,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A8,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Available</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="I8" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A8,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>None needed</v>
+      </c>
+      <c r="K8" s="37" t="s">
+        <v>605</v>
+      </c>
+      <c r="L8" s="37" t="n">
+        <f aca="false">'Control Map'!M10</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="G9" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A9,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A9,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Partial</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="I9" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A9,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-06</v>
+      </c>
+      <c r="K9" s="37" t="s">
+        <v>610</v>
+      </c>
+      <c r="L9" s="37" t="str">
+        <f aca="false">IF(L7=L8,"Yes","No: check rows")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="G10" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A10,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A10,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Available</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="I10" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A10,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>None needed</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>615</v>
+      </c>
+      <c r="L10" s="37" t="n">
+        <f aca="false">COUNTIF($I$4:$I$60,"GAP-*")</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="G11" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A11,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A11,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Partial</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="I11" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A11,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-08</v>
+      </c>
+      <c r="K11" s="37" t="s">
+        <v>620</v>
+      </c>
+      <c r="L11" s="37" t="n">
+        <f aca="false">'Control Map'!M12</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="G12" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A12,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A12,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Partial</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="I12" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A12,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-01</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="G13" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A13,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A13,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Missing</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="I13" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A13,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-12</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="G14" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A14,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A14,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Partial</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="I14" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A14,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-21</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="G15" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A15,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A15,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Partial</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="I15" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A15,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-02</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="G16" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A16,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A16,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Missing</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="I16" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A16,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-20</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="G17" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A17,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A17,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Partial</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="I17" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A17,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-11</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="G18" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A18,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A18,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Partial</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="I18" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A18,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-03</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="G19" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A19,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A19,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Missing</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="I19" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A19,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-04</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="G20" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A20,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A20,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Partial</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="I20" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A20,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-05</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="G21" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A21,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A21,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Partial</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="I21" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A21,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-07</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="G22" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A22,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A22,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Missing</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="I22" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A22,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-18</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="G23" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A23,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A23,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Missing</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="I23" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A23,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-19</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="G24" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A24,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A24,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Missing</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="I24" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A24,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-15</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>670</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="G25" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A25,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A25,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Missing</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="I25" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A25,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-16</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>674</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="G26" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A26,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A26,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Missing</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="I26" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A26,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-09</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="G27" s="6" t="str">
+        <f aca="false">IF(INDEX('Control Map'!$E$4:$E$60,MATCH(A27,'Control Map'!$C$4:$C$60,0))="Implemented","Available",INDEX('Control Map'!$E$4:$E$60,MATCH(A27,'Control Map'!$C$4:$C$60,0)))</f>
+        <v>Missing</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="I27" s="6" t="str">
+        <f aca="false">IFERROR(INDEX('Remediation Plan'!$A$4:$A$60,MATCH(A27,'Remediation Plan'!$D$4:$D$60,0)),"None needed")</f>
+        <v>GAP-10</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:I27"/>
+  <conditionalFormatting sqref="G4:G60">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+      <formula>"Available"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+      <formula>"Partial"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+      <formula>"Missing"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G4:G60" type="list">
       <formula1>"Available,Partial,Missing"</formula1>
@@ -6167,5 +8223,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>